--- a/public/Project files/userInfo/userInfo.xlsx
+++ b/public/Project files/userInfo/userInfo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 Hansoll AI\Hansoll AI Portal TEST2\public\Project files\userInfo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\RPA TEST\IT\AI Gallery\2. UserInfo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251472C9-80B7-43E5-9131-283D007FD10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71F1B613-4C87-4E42-B9DE-2080BA713F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="825" windowWidth="24405" windowHeight="14235" xr2:uid="{AC4F52AC-37CD-4E1C-B6CD-13B060276440}"/>
+    <workbookView xWindow="34200" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{AC4F52AC-37CD-4E1C-B6CD-13B060276440}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6948" uniqueCount="2472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6369" uniqueCount="2470">
   <si>
     <t>EMP_NO</t>
   </si>
@@ -7449,14 +7449,6 @@
   </si>
   <si>
     <t>ywkim1@hansoll.com</t>
-  </si>
-  <si>
-    <t>CL_COMPANY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>본사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7855,7 +7847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC851950-8F08-4E5F-9B24-71F37F57CA13}">
-  <dimension ref="A1:L579"/>
+  <dimension ref="A1:K579"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.75" style="2" customWidth="1"/>
@@ -7869,11 +7861,10 @@
     <col min="9" max="9" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7907,11 +7898,8 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -7945,11 +7933,8 @@
       <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -7983,11 +7968,8 @@
       <c r="K3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -8021,11 +8003,8 @@
       <c r="K4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
@@ -8059,11 +8038,8 @@
       <c r="K5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -8097,11 +8073,8 @@
       <c r="K6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -8135,11 +8108,8 @@
       <c r="K7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
@@ -8173,11 +8143,8 @@
       <c r="K8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
@@ -8211,11 +8178,8 @@
       <c r="K9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
@@ -8249,11 +8213,8 @@
       <c r="K10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>65</v>
       </c>
@@ -8287,11 +8248,8 @@
       <c r="K11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -8325,11 +8283,8 @@
       <c r="K12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>75</v>
       </c>
@@ -8363,11 +8318,8 @@
       <c r="K13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -8401,11 +8353,8 @@
       <c r="K14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>87</v>
       </c>
@@ -8439,11 +8388,8 @@
       <c r="K15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>91</v>
       </c>
@@ -8477,11 +8423,8 @@
       <c r="K16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>95</v>
       </c>
@@ -8515,11 +8458,8 @@
       <c r="K17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>99</v>
       </c>
@@ -8553,11 +8493,8 @@
       <c r="K18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>103</v>
       </c>
@@ -8591,11 +8528,8 @@
       <c r="K19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>107</v>
       </c>
@@ -8629,11 +8563,8 @@
       <c r="K20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>111</v>
       </c>
@@ -8667,11 +8598,8 @@
       <c r="K21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>115</v>
       </c>
@@ -8705,11 +8633,8 @@
       <c r="K22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>121</v>
       </c>
@@ -8743,11 +8668,8 @@
       <c r="K23" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>130</v>
       </c>
@@ -8781,11 +8703,8 @@
       <c r="K24" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>136</v>
       </c>
@@ -8819,11 +8738,8 @@
       <c r="K25" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>140</v>
       </c>
@@ -8857,11 +8773,8 @@
       <c r="K26" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>146</v>
       </c>
@@ -8895,11 +8808,8 @@
       <c r="K27" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>150</v>
       </c>
@@ -8933,11 +8843,8 @@
       <c r="K28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>156</v>
       </c>
@@ -8971,11 +8878,8 @@
       <c r="K29" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>160</v>
       </c>
@@ -9009,11 +8913,8 @@
       <c r="K30" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>164</v>
       </c>
@@ -9047,11 +8948,8 @@
       <c r="K31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>170</v>
       </c>
@@ -9085,11 +8983,8 @@
       <c r="K32" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>175</v>
       </c>
@@ -9123,11 +9018,8 @@
       <c r="K33" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>179</v>
       </c>
@@ -9161,11 +9053,8 @@
       <c r="K34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>186</v>
       </c>
@@ -9199,11 +9088,8 @@
       <c r="K35" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>192</v>
       </c>
@@ -9237,11 +9123,8 @@
       <c r="K36" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>196</v>
       </c>
@@ -9275,11 +9158,8 @@
       <c r="K37" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>202</v>
       </c>
@@ -9313,11 +9193,8 @@
       <c r="K38" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>208</v>
       </c>
@@ -9351,11 +9228,8 @@
       <c r="K39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>212</v>
       </c>
@@ -9389,11 +9263,8 @@
       <c r="K40" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>216</v>
       </c>
@@ -9427,11 +9298,8 @@
       <c r="K41" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>220</v>
       </c>
@@ -9465,11 +9333,8 @@
       <c r="K42" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -9503,11 +9368,8 @@
       <c r="K43" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>228</v>
       </c>
@@ -9541,11 +9403,8 @@
       <c r="K44" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>232</v>
       </c>
@@ -9579,11 +9438,8 @@
       <c r="K45" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>236</v>
       </c>
@@ -9617,11 +9473,8 @@
       <c r="K46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>240</v>
       </c>
@@ -9655,11 +9508,8 @@
       <c r="K47" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>244</v>
       </c>
@@ -9693,11 +9543,8 @@
       <c r="K48" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>250</v>
       </c>
@@ -9731,11 +9578,8 @@
       <c r="K49" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>254</v>
       </c>
@@ -9769,11 +9613,8 @@
       <c r="K50" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>258</v>
       </c>
@@ -9807,11 +9648,8 @@
       <c r="K51" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>264</v>
       </c>
@@ -9845,11 +9683,8 @@
       <c r="K52" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>268</v>
       </c>
@@ -9883,11 +9718,8 @@
       <c r="K53" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>272</v>
       </c>
@@ -9921,11 +9753,8 @@
       <c r="K54" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>276</v>
       </c>
@@ -9959,11 +9788,8 @@
       <c r="K55" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>280</v>
       </c>
@@ -9997,11 +9823,8 @@
       <c r="K56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L56" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>284</v>
       </c>
@@ -10035,11 +9858,8 @@
       <c r="K57" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>288</v>
       </c>
@@ -10073,11 +9893,8 @@
       <c r="K58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>292</v>
       </c>
@@ -10111,11 +9928,8 @@
       <c r="K59" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>298</v>
       </c>
@@ -10149,11 +9963,8 @@
       <c r="K60" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L60" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>302</v>
       </c>
@@ -10187,11 +9998,8 @@
       <c r="K61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L61" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>306</v>
       </c>
@@ -10225,11 +10033,8 @@
       <c r="K62" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>312</v>
       </c>
@@ -10263,11 +10068,8 @@
       <c r="K63" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>316</v>
       </c>
@@ -10301,11 +10103,8 @@
       <c r="K64" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L64" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>320</v>
       </c>
@@ -10339,11 +10138,8 @@
       <c r="K65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L65" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>324</v>
       </c>
@@ -10377,11 +10173,8 @@
       <c r="K66" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L66" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>328</v>
       </c>
@@ -10415,11 +10208,8 @@
       <c r="K67" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L67" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>332</v>
       </c>
@@ -10453,11 +10243,8 @@
       <c r="K68" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>336</v>
       </c>
@@ -10491,11 +10278,8 @@
       <c r="K69" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L69" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>340</v>
       </c>
@@ -10529,11 +10313,8 @@
       <c r="K70" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>344</v>
       </c>
@@ -10567,11 +10348,8 @@
       <c r="K71" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>348</v>
       </c>
@@ -10605,11 +10383,8 @@
       <c r="K72" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L72" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>352</v>
       </c>
@@ -10643,11 +10418,8 @@
       <c r="K73" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>356</v>
       </c>
@@ -10681,11 +10453,8 @@
       <c r="K74" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L74" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>362</v>
       </c>
@@ -10719,11 +10488,8 @@
       <c r="K75" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>366</v>
       </c>
@@ -10757,11 +10523,8 @@
       <c r="K76" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>370</v>
       </c>
@@ -10795,11 +10558,8 @@
       <c r="K77" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>374</v>
       </c>
@@ -10833,11 +10593,8 @@
       <c r="K78" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L78" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>378</v>
       </c>
@@ -10871,11 +10628,8 @@
       <c r="K79" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L79" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>382</v>
       </c>
@@ -10909,11 +10663,8 @@
       <c r="K80" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L80" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>386</v>
       </c>
@@ -10947,11 +10698,8 @@
       <c r="K81" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L81" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>390</v>
       </c>
@@ -10985,11 +10733,8 @@
       <c r="K82" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L82" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>394</v>
       </c>
@@ -11023,11 +10768,8 @@
       <c r="K83" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L83" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>400</v>
       </c>
@@ -11061,11 +10803,8 @@
       <c r="K84" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L84" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>404</v>
       </c>
@@ -11099,11 +10838,8 @@
       <c r="K85" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>408</v>
       </c>
@@ -11137,11 +10873,8 @@
       <c r="K86" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>414</v>
       </c>
@@ -11175,11 +10908,8 @@
       <c r="K87" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L87" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>418</v>
       </c>
@@ -11213,11 +10943,8 @@
       <c r="K88" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>422</v>
       </c>
@@ -11251,11 +10978,8 @@
       <c r="K89" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L89" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>426</v>
       </c>
@@ -11289,11 +11013,8 @@
       <c r="K90" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L90" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>430</v>
       </c>
@@ -11327,11 +11048,8 @@
       <c r="K91" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L91" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>434</v>
       </c>
@@ -11365,11 +11083,8 @@
       <c r="K92" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L92" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>438</v>
       </c>
@@ -11403,11 +11118,8 @@
       <c r="K93" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L93" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>442</v>
       </c>
@@ -11441,11 +11153,8 @@
       <c r="K94" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>448</v>
       </c>
@@ -11479,11 +11188,8 @@
       <c r="K95" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L95" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>452</v>
       </c>
@@ -11517,11 +11223,8 @@
       <c r="K96" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L96" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>455</v>
       </c>
@@ -11555,11 +11258,8 @@
       <c r="K97" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L97" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>459</v>
       </c>
@@ -11593,11 +11293,8 @@
       <c r="K98" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L98" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>463</v>
       </c>
@@ -11631,11 +11328,8 @@
       <c r="K99" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L99" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>469</v>
       </c>
@@ -11669,11 +11363,8 @@
       <c r="K100" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L100" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>473</v>
       </c>
@@ -11707,11 +11398,8 @@
       <c r="K101" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L101" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>477</v>
       </c>
@@ -11745,11 +11433,8 @@
       <c r="K102" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L102" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>481</v>
       </c>
@@ -11783,11 +11468,8 @@
       <c r="K103" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L103" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>485</v>
       </c>
@@ -11821,11 +11503,8 @@
       <c r="K104" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L104" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>489</v>
       </c>
@@ -11859,11 +11538,8 @@
       <c r="K105" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L105" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>492</v>
       </c>
@@ -11897,11 +11573,8 @@
       <c r="K106" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L106" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>496</v>
       </c>
@@ -11935,11 +11608,8 @@
       <c r="K107" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L107" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>502</v>
       </c>
@@ -11973,11 +11643,8 @@
       <c r="K108" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L108" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>506</v>
       </c>
@@ -12011,11 +11678,8 @@
       <c r="K109" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L109" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>510</v>
       </c>
@@ -12049,11 +11713,8 @@
       <c r="K110" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L110" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>514</v>
       </c>
@@ -12087,11 +11748,8 @@
       <c r="K111" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L111" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>518</v>
       </c>
@@ -12125,11 +11783,8 @@
       <c r="K112" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L112" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>522</v>
       </c>
@@ -12163,11 +11818,8 @@
       <c r="K113" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>526</v>
       </c>
@@ -12201,11 +11853,8 @@
       <c r="K114" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>530</v>
       </c>
@@ -12239,11 +11888,8 @@
       <c r="K115" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L115" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>534</v>
       </c>
@@ -12277,11 +11923,8 @@
       <c r="K116" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L116" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>538</v>
       </c>
@@ -12315,11 +11958,8 @@
       <c r="K117" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L117" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>542</v>
       </c>
@@ -12353,11 +11993,8 @@
       <c r="K118" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L118" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>546</v>
       </c>
@@ -12391,11 +12028,8 @@
       <c r="K119" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L119" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>552</v>
       </c>
@@ -12429,11 +12063,8 @@
       <c r="K120" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L120" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>556</v>
       </c>
@@ -12467,11 +12098,8 @@
       <c r="K121" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L121" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>560</v>
       </c>
@@ -12505,11 +12133,8 @@
       <c r="K122" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>567</v>
       </c>
@@ -12543,11 +12168,8 @@
       <c r="K123" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L123" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>571</v>
       </c>
@@ -12581,11 +12203,8 @@
       <c r="K124" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>575</v>
       </c>
@@ -12619,11 +12238,8 @@
       <c r="K125" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L125" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>579</v>
       </c>
@@ -12657,11 +12273,8 @@
       <c r="K126" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L126" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>583</v>
       </c>
@@ -12695,11 +12308,8 @@
       <c r="K127" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L127" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>587</v>
       </c>
@@ -12733,11 +12343,8 @@
       <c r="K128" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L128" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>591</v>
       </c>
@@ -12771,11 +12378,8 @@
       <c r="K129" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L129" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>595</v>
       </c>
@@ -12809,11 +12413,8 @@
       <c r="K130" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L130" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>599</v>
       </c>
@@ -12847,11 +12448,8 @@
       <c r="K131" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L131" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>603</v>
       </c>
@@ -12885,11 +12483,8 @@
       <c r="K132" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L132" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>607</v>
       </c>
@@ -12923,11 +12518,8 @@
       <c r="K133" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L133" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>613</v>
       </c>
@@ -12961,11 +12553,8 @@
       <c r="K134" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L134" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>617</v>
       </c>
@@ -12999,11 +12588,8 @@
       <c r="K135" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L135" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>621</v>
       </c>
@@ -13037,11 +12623,8 @@
       <c r="K136" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L136" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>625</v>
       </c>
@@ -13075,11 +12658,8 @@
       <c r="K137" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L137" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>629</v>
       </c>
@@ -13113,11 +12693,8 @@
       <c r="K138" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L138" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>633</v>
       </c>
@@ -13151,11 +12728,8 @@
       <c r="K139" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L139" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>637</v>
       </c>
@@ -13189,11 +12763,8 @@
       <c r="K140" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L140" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>640</v>
       </c>
@@ -13227,11 +12798,8 @@
       <c r="K141" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L141" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>646</v>
       </c>
@@ -13265,11 +12833,8 @@
       <c r="K142" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L142" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>650</v>
       </c>
@@ -13303,11 +12868,8 @@
       <c r="K143" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L143" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>654</v>
       </c>
@@ -13341,11 +12903,8 @@
       <c r="K144" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L144" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>658</v>
       </c>
@@ -13379,11 +12938,8 @@
       <c r="K145" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L145" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>662</v>
       </c>
@@ -13417,11 +12973,8 @@
       <c r="K146" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L146" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>666</v>
       </c>
@@ -13455,11 +13008,8 @@
       <c r="K147" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L147" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>670</v>
       </c>
@@ -13493,11 +13043,8 @@
       <c r="K148" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L148" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>674</v>
       </c>
@@ -13531,11 +13078,8 @@
       <c r="K149" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L149" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>678</v>
       </c>
@@ -13569,11 +13113,8 @@
       <c r="K150" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L150" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>682</v>
       </c>
@@ -13607,11 +13148,8 @@
       <c r="K151" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L151" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>686</v>
       </c>
@@ -13645,11 +13183,8 @@
       <c r="K152" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L152" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>690</v>
       </c>
@@ -13683,11 +13218,8 @@
       <c r="K153" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L153" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>694</v>
       </c>
@@ -13721,11 +13253,8 @@
       <c r="K154" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L154" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>698</v>
       </c>
@@ -13759,11 +13288,8 @@
       <c r="K155" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L155" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>702</v>
       </c>
@@ -13797,11 +13323,8 @@
       <c r="K156" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L156" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>706</v>
       </c>
@@ -13835,11 +13358,8 @@
       <c r="K157" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L157" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>710</v>
       </c>
@@ -13873,11 +13393,8 @@
       <c r="K158" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L158" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>714</v>
       </c>
@@ -13911,11 +13428,8 @@
       <c r="K159" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L159" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>720</v>
       </c>
@@ -13949,11 +13463,8 @@
       <c r="K160" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L160" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>724</v>
       </c>
@@ -13987,11 +13498,8 @@
       <c r="K161" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L161" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>728</v>
       </c>
@@ -14025,11 +13533,8 @@
       <c r="K162" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L162" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>732</v>
       </c>
@@ -14063,11 +13568,8 @@
       <c r="K163" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L163" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>738</v>
       </c>
@@ -14101,11 +13603,8 @@
       <c r="K164" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L164" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>742</v>
       </c>
@@ -14139,11 +13638,8 @@
       <c r="K165" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L165" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>748</v>
       </c>
@@ -14177,11 +13673,8 @@
       <c r="K166" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L166" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>752</v>
       </c>
@@ -14215,11 +13708,8 @@
       <c r="K167" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L167" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>756</v>
       </c>
@@ -14253,11 +13743,8 @@
       <c r="K168" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L168" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>760</v>
       </c>
@@ -14291,11 +13778,8 @@
       <c r="K169" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L169" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>764</v>
       </c>
@@ -14329,11 +13813,8 @@
       <c r="K170" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L170" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>768</v>
       </c>
@@ -14367,11 +13848,8 @@
       <c r="K171" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L171" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>772</v>
       </c>
@@ -14405,11 +13883,8 @@
       <c r="K172" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L172" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>776</v>
       </c>
@@ -14443,11 +13918,8 @@
       <c r="K173" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L173" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>780</v>
       </c>
@@ -14481,11 +13953,8 @@
       <c r="K174" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L174" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>784</v>
       </c>
@@ -14519,11 +13988,8 @@
       <c r="K175" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L175" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>788</v>
       </c>
@@ -14557,11 +14023,8 @@
       <c r="K176" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L176" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>792</v>
       </c>
@@ -14595,11 +14058,8 @@
       <c r="K177" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L177" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>796</v>
       </c>
@@ -14633,11 +14093,8 @@
       <c r="K178" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L178" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>800</v>
       </c>
@@ -14671,11 +14128,8 @@
       <c r="K179" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L179" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>804</v>
       </c>
@@ -14709,11 +14163,8 @@
       <c r="K180" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L180" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>808</v>
       </c>
@@ -14747,11 +14198,8 @@
       <c r="K181" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L181" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>812</v>
       </c>
@@ -14785,11 +14233,8 @@
       <c r="K182" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L182" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>816</v>
       </c>
@@ -14823,11 +14268,8 @@
       <c r="K183" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L183" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>820</v>
       </c>
@@ -14861,11 +14303,8 @@
       <c r="K184" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L184" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>824</v>
       </c>
@@ -14899,11 +14338,8 @@
       <c r="K185" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L185" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>828</v>
       </c>
@@ -14937,11 +14373,8 @@
       <c r="K186" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L186" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>832</v>
       </c>
@@ -14975,11 +14408,8 @@
       <c r="K187" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L187" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>838</v>
       </c>
@@ -15013,11 +14443,8 @@
       <c r="K188" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L188" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>842</v>
       </c>
@@ -15051,11 +14478,8 @@
       <c r="K189" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L189" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>846</v>
       </c>
@@ -15089,11 +14513,8 @@
       <c r="K190" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L190" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>850</v>
       </c>
@@ -15127,11 +14548,8 @@
       <c r="K191" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L191" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>854</v>
       </c>
@@ -15165,11 +14583,8 @@
       <c r="K192" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L192" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>858</v>
       </c>
@@ -15203,11 +14618,8 @@
       <c r="K193" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L193" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>862</v>
       </c>
@@ -15241,11 +14653,8 @@
       <c r="K194" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L194" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>868</v>
       </c>
@@ -15279,11 +14688,8 @@
       <c r="K195" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L195" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>872</v>
       </c>
@@ -15317,11 +14723,8 @@
       <c r="K196" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L196" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>876</v>
       </c>
@@ -15355,11 +14758,8 @@
       <c r="K197" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L197" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>880</v>
       </c>
@@ -15393,11 +14793,8 @@
       <c r="K198" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L198" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>884</v>
       </c>
@@ -15431,11 +14828,8 @@
       <c r="K199" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L199" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>888</v>
       </c>
@@ -15469,11 +14863,8 @@
       <c r="K200" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L200" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>892</v>
       </c>
@@ -15507,11 +14898,8 @@
       <c r="K201" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L201" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>896</v>
       </c>
@@ -15545,11 +14933,8 @@
       <c r="K202" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L202" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>900</v>
       </c>
@@ -15583,11 +14968,8 @@
       <c r="K203" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L203" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>904</v>
       </c>
@@ -15621,11 +15003,8 @@
       <c r="K204" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L204" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>908</v>
       </c>
@@ -15659,11 +15038,8 @@
       <c r="K205" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L205" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>912</v>
       </c>
@@ -15697,11 +15073,8 @@
       <c r="K206" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L206" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>918</v>
       </c>
@@ -15735,11 +15108,8 @@
       <c r="K207" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L207" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>921</v>
       </c>
@@ -15773,11 +15143,8 @@
       <c r="K208" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L208" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>925</v>
       </c>
@@ -15811,11 +15178,8 @@
       <c r="K209" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L209" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>929</v>
       </c>
@@ -15849,11 +15213,8 @@
       <c r="K210" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L210" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>933</v>
       </c>
@@ -15887,11 +15248,8 @@
       <c r="K211" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L211" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>937</v>
       </c>
@@ -15925,11 +15283,8 @@
       <c r="K212" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L212" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>941</v>
       </c>
@@ -15963,11 +15318,8 @@
       <c r="K213" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L213" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>945</v>
       </c>
@@ -16001,11 +15353,8 @@
       <c r="K214" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L214" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>949</v>
       </c>
@@ -16039,11 +15388,8 @@
       <c r="K215" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L215" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>953</v>
       </c>
@@ -16077,11 +15423,8 @@
       <c r="K216" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L216" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>959</v>
       </c>
@@ -16115,11 +15458,8 @@
       <c r="K217" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L217" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>963</v>
       </c>
@@ -16153,11 +15493,8 @@
       <c r="K218" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L218" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>967</v>
       </c>
@@ -16191,11 +15528,8 @@
       <c r="K219" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L219" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>971</v>
       </c>
@@ -16229,11 +15563,8 @@
       <c r="K220" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L220" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>975</v>
       </c>
@@ -16267,11 +15598,8 @@
       <c r="K221" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L221" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>979</v>
       </c>
@@ -16305,11 +15633,8 @@
       <c r="K222" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L222" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>983</v>
       </c>
@@ -16343,11 +15668,8 @@
       <c r="K223" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L223" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>989</v>
       </c>
@@ -16381,11 +15703,8 @@
       <c r="K224" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L224" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>993</v>
       </c>
@@ -16419,11 +15738,8 @@
       <c r="K225" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L225" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>997</v>
       </c>
@@ -16457,11 +15773,8 @@
       <c r="K226" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L226" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>1001</v>
       </c>
@@ -16495,11 +15808,8 @@
       <c r="K227" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L227" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>1005</v>
       </c>
@@ -16533,11 +15843,8 @@
       <c r="K228" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L228" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>1011</v>
       </c>
@@ -16571,11 +15878,8 @@
       <c r="K229" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L229" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>1015</v>
       </c>
@@ -16609,11 +15913,8 @@
       <c r="K230" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L230" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>1019</v>
       </c>
@@ -16647,11 +15948,8 @@
       <c r="K231" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L231" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>1025</v>
       </c>
@@ -16685,11 +15983,8 @@
       <c r="K232" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L232" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>1029</v>
       </c>
@@ -16723,11 +16018,8 @@
       <c r="K233" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L233" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>1033</v>
       </c>
@@ -16761,11 +16053,8 @@
       <c r="K234" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L234" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>1037</v>
       </c>
@@ -16799,11 +16088,8 @@
       <c r="K235" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L235" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>1041</v>
       </c>
@@ -16837,11 +16123,8 @@
       <c r="K236" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L236" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>1045</v>
       </c>
@@ -16875,11 +16158,8 @@
       <c r="K237" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L237" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>1051</v>
       </c>
@@ -16913,11 +16193,8 @@
       <c r="K238" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L238" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>1054</v>
       </c>
@@ -16951,11 +16228,8 @@
       <c r="K239" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L239" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>1058</v>
       </c>
@@ -16989,11 +16263,8 @@
       <c r="K240" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L240" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>1064</v>
       </c>
@@ -17027,11 +16298,8 @@
       <c r="K241" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L241" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>1068</v>
       </c>
@@ -17065,11 +16333,8 @@
       <c r="K242" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L242" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>1072</v>
       </c>
@@ -17103,11 +16368,8 @@
       <c r="K243" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L243" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>1078</v>
       </c>
@@ -17141,11 +16403,8 @@
       <c r="K244" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L244" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>1084</v>
       </c>
@@ -17179,11 +16438,8 @@
       <c r="K245" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L245" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>1088</v>
       </c>
@@ -17217,11 +16473,8 @@
       <c r="K246" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L246" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>1092</v>
       </c>
@@ -17255,11 +16508,8 @@
       <c r="K247" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L247" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>1096</v>
       </c>
@@ -17293,11 +16543,8 @@
       <c r="K248" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L248" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>1100</v>
       </c>
@@ -17331,11 +16578,8 @@
       <c r="K249" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L249" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>1106</v>
       </c>
@@ -17369,11 +16613,8 @@
       <c r="K250" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L250" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>1110</v>
       </c>
@@ -17407,11 +16648,8 @@
       <c r="K251" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L251" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>1114</v>
       </c>
@@ -17445,11 +16683,8 @@
       <c r="K252" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L252" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>1118</v>
       </c>
@@ -17483,11 +16718,8 @@
       <c r="K253" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L253" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>1122</v>
       </c>
@@ -17521,11 +16753,8 @@
       <c r="K254" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L254" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>1128</v>
       </c>
@@ -17559,11 +16788,8 @@
       <c r="K255" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L255" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>1132</v>
       </c>
@@ -17597,11 +16823,8 @@
       <c r="K256" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L256" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>1136</v>
       </c>
@@ -17635,11 +16858,8 @@
       <c r="K257" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L257" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>1140</v>
       </c>
@@ -17673,11 +16893,8 @@
       <c r="K258" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L258" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>1144</v>
       </c>
@@ -17711,11 +16928,8 @@
       <c r="K259" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L259" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>1148</v>
       </c>
@@ -17749,11 +16963,8 @@
       <c r="K260" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L260" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>1154</v>
       </c>
@@ -17787,11 +16998,8 @@
       <c r="K261" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L261" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>1158</v>
       </c>
@@ -17825,11 +17033,8 @@
       <c r="K262" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L262" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>1162</v>
       </c>
@@ -17863,11 +17068,8 @@
       <c r="K263" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L263" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>1166</v>
       </c>
@@ -17901,11 +17103,8 @@
       <c r="K264" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L264" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>1170</v>
       </c>
@@ -17939,11 +17138,8 @@
       <c r="K265" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L265" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>1174</v>
       </c>
@@ -17977,11 +17173,8 @@
       <c r="K266" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L266" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>1178</v>
       </c>
@@ -18015,11 +17208,8 @@
       <c r="K267" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L267" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>1182</v>
       </c>
@@ -18053,11 +17243,8 @@
       <c r="K268" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L268" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18091,11 +17278,8 @@
       <c r="K269" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L269" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>1190</v>
       </c>
@@ -18129,11 +17313,8 @@
       <c r="K270" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L270" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>1196</v>
       </c>
@@ -18167,11 +17348,8 @@
       <c r="K271" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L271" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>1200</v>
       </c>
@@ -18205,11 +17383,8 @@
       <c r="K272" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L272" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>1204</v>
       </c>
@@ -18243,11 +17418,8 @@
       <c r="K273" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L273" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>1208</v>
       </c>
@@ -18281,11 +17453,8 @@
       <c r="K274" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L274" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>1212</v>
       </c>
@@ -18319,11 +17488,8 @@
       <c r="K275" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L275" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>1216</v>
       </c>
@@ -18357,11 +17523,8 @@
       <c r="K276" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L276" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>1220</v>
       </c>
@@ -18395,11 +17558,8 @@
       <c r="K277" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L277" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>1226</v>
       </c>
@@ -18433,11 +17593,8 @@
       <c r="K278" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L278" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>1230</v>
       </c>
@@ -18471,11 +17628,8 @@
       <c r="K279" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L279" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>1234</v>
       </c>
@@ -18509,11 +17663,8 @@
       <c r="K280" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L280" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>1238</v>
       </c>
@@ -18547,11 +17698,8 @@
       <c r="K281" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L281" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>1242</v>
       </c>
@@ -18585,11 +17733,8 @@
       <c r="K282" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L282" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>1246</v>
       </c>
@@ -18623,11 +17768,8 @@
       <c r="K283" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L283" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>1249</v>
       </c>
@@ -18661,11 +17803,8 @@
       <c r="K284" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L284" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>1253</v>
       </c>
@@ -18699,11 +17838,8 @@
       <c r="K285" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L285" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>1257</v>
       </c>
@@ -18737,11 +17873,8 @@
       <c r="K286" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L286" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>1261</v>
       </c>
@@ -18775,11 +17908,8 @@
       <c r="K287" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L287" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>1265</v>
       </c>
@@ -18813,11 +17943,8 @@
       <c r="K288" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L288" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>1269</v>
       </c>
@@ -18851,11 +17978,8 @@
       <c r="K289" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L289" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>1273</v>
       </c>
@@ -18889,11 +18013,8 @@
       <c r="K290" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L290" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>1277</v>
       </c>
@@ -18927,11 +18048,8 @@
       <c r="K291" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L291" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>1281</v>
       </c>
@@ -18965,11 +18083,8 @@
       <c r="K292" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L292" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>1285</v>
       </c>
@@ -19003,11 +18118,8 @@
       <c r="K293" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L293" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>1289</v>
       </c>
@@ -19041,11 +18153,8 @@
       <c r="K294" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L294" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>1293</v>
       </c>
@@ -19079,11 +18188,8 @@
       <c r="K295" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L295" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>1297</v>
       </c>
@@ -19117,11 +18223,8 @@
       <c r="K296" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L296" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>1301</v>
       </c>
@@ -19155,11 +18258,8 @@
       <c r="K297" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L297" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>1305</v>
       </c>
@@ -19193,11 +18293,8 @@
       <c r="K298" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L298" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>1311</v>
       </c>
@@ -19231,11 +18328,8 @@
       <c r="K299" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L299" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>1315</v>
       </c>
@@ -19269,11 +18363,8 @@
       <c r="K300" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L300" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>1319</v>
       </c>
@@ -19307,11 +18398,8 @@
       <c r="K301" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L301" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>1323</v>
       </c>
@@ -19345,11 +18433,8 @@
       <c r="K302" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L302" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>1327</v>
       </c>
@@ -19383,11 +18468,8 @@
       <c r="K303" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L303" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>1331</v>
       </c>
@@ -19421,11 +18503,8 @@
       <c r="K304" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L304" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>1335</v>
       </c>
@@ -19459,11 +18538,8 @@
       <c r="K305" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L305" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>1341</v>
       </c>
@@ -19497,11 +18573,8 @@
       <c r="K306" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L306" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>1345</v>
       </c>
@@ -19535,11 +18608,8 @@
       <c r="K307" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L307" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>1349</v>
       </c>
@@ -19573,11 +18643,8 @@
       <c r="K308" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L308" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>1353</v>
       </c>
@@ -19611,11 +18678,8 @@
       <c r="K309" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L309" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>1357</v>
       </c>
@@ -19649,11 +18713,8 @@
       <c r="K310" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L310" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>1361</v>
       </c>
@@ -19687,11 +18748,8 @@
       <c r="K311" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L311" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>1365</v>
       </c>
@@ -19725,11 +18783,8 @@
       <c r="K312" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L312" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>1369</v>
       </c>
@@ -19763,11 +18818,8 @@
       <c r="K313" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L313" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>1373</v>
       </c>
@@ -19801,11 +18853,8 @@
       <c r="K314" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L314" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>1379</v>
       </c>
@@ -19839,11 +18888,8 @@
       <c r="K315" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L315" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>1383</v>
       </c>
@@ -19877,11 +18923,8 @@
       <c r="K316" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L316" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>1387</v>
       </c>
@@ -19915,11 +18958,8 @@
       <c r="K317" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L317" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>1391</v>
       </c>
@@ -19953,11 +18993,8 @@
       <c r="K318" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L318" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>1395</v>
       </c>
@@ -19991,11 +19028,8 @@
       <c r="K319" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L319" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>1399</v>
       </c>
@@ -20029,11 +19063,8 @@
       <c r="K320" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L320" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>1403</v>
       </c>
@@ -20067,11 +19098,8 @@
       <c r="K321" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L321" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>1407</v>
       </c>
@@ -20105,11 +19133,8 @@
       <c r="K322" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L322" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>1411</v>
       </c>
@@ -20143,11 +19168,8 @@
       <c r="K323" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L323" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>1415</v>
       </c>
@@ -20181,11 +19203,8 @@
       <c r="K324" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L324" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>1419</v>
       </c>
@@ -20219,11 +19238,8 @@
       <c r="K325" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L325" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>1422</v>
       </c>
@@ -20257,11 +19273,8 @@
       <c r="K326" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L326" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>1426</v>
       </c>
@@ -20295,11 +19308,8 @@
       <c r="K327" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L327" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>1429</v>
       </c>
@@ -20333,11 +19343,8 @@
       <c r="K328" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L328" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>1432</v>
       </c>
@@ -20371,11 +19378,8 @@
       <c r="K329" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L329" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>1436</v>
       </c>
@@ -20409,11 +19413,8 @@
       <c r="K330" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L330" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>1442</v>
       </c>
@@ -20447,11 +19448,8 @@
       <c r="K331" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L331" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>1446</v>
       </c>
@@ -20485,11 +19483,8 @@
       <c r="K332" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L332" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>1452</v>
       </c>
@@ -20523,11 +19518,8 @@
       <c r="K333" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L333" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>1456</v>
       </c>
@@ -20561,11 +19553,8 @@
       <c r="K334" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L334" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>1460</v>
       </c>
@@ -20599,11 +19588,8 @@
       <c r="K335" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L335" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>1464</v>
       </c>
@@ -20637,11 +19623,8 @@
       <c r="K336" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L336" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>1468</v>
       </c>
@@ -20675,11 +19658,8 @@
       <c r="K337" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L337" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>1472</v>
       </c>
@@ -20713,11 +19693,8 @@
       <c r="K338" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L338" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>1476</v>
       </c>
@@ -20751,11 +19728,8 @@
       <c r="K339" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L339" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>1480</v>
       </c>
@@ -20789,11 +19763,8 @@
       <c r="K340" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L340" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>1484</v>
       </c>
@@ -20827,11 +19798,8 @@
       <c r="K341" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L341" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>1488</v>
       </c>
@@ -20865,11 +19833,8 @@
       <c r="K342" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L342" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>1492</v>
       </c>
@@ -20903,11 +19868,8 @@
       <c r="K343" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L343" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>1496</v>
       </c>
@@ -20941,11 +19903,8 @@
       <c r="K344" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L344" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>1500</v>
       </c>
@@ -20979,11 +19938,8 @@
       <c r="K345" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L345" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>1504</v>
       </c>
@@ -21017,11 +19973,8 @@
       <c r="K346" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L346" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>1508</v>
       </c>
@@ -21055,11 +20008,8 @@
       <c r="K347" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L347" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>1512</v>
       </c>
@@ -21093,11 +20043,8 @@
       <c r="K348" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L348" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>1516</v>
       </c>
@@ -21131,11 +20078,8 @@
       <c r="K349" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L349" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>1522</v>
       </c>
@@ -21169,11 +20113,8 @@
       <c r="K350" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L350" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>1526</v>
       </c>
@@ -21207,11 +20148,8 @@
       <c r="K351" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L351" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>1530</v>
       </c>
@@ -21245,11 +20183,8 @@
       <c r="K352" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L352" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>1534</v>
       </c>
@@ -21283,11 +20218,8 @@
       <c r="K353" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L353" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>1538</v>
       </c>
@@ -21321,11 +20253,8 @@
       <c r="K354" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L354" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>1542</v>
       </c>
@@ -21359,11 +20288,8 @@
       <c r="K355" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L355" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>1546</v>
       </c>
@@ -21397,11 +20323,8 @@
       <c r="K356" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L356" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>1550</v>
       </c>
@@ -21435,11 +20358,8 @@
       <c r="K357" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L357" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>1554</v>
       </c>
@@ -21473,11 +20393,8 @@
       <c r="K358" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L358" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>1558</v>
       </c>
@@ -21511,11 +20428,8 @@
       <c r="K359" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L359" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>1562</v>
       </c>
@@ -21549,11 +20463,8 @@
       <c r="K360" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L360" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>1566</v>
       </c>
@@ -21587,11 +20498,8 @@
       <c r="K361" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L361" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>1570</v>
       </c>
@@ -21625,11 +20533,8 @@
       <c r="K362" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L362" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>1574</v>
       </c>
@@ -21663,11 +20568,8 @@
       <c r="K363" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L363" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>1578</v>
       </c>
@@ -21701,11 +20603,8 @@
       <c r="K364" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L364" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>1582</v>
       </c>
@@ -21739,11 +20638,8 @@
       <c r="K365" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L365" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>1586</v>
       </c>
@@ -21777,11 +20673,8 @@
       <c r="K366" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L366" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>1589</v>
       </c>
@@ -21815,11 +20708,8 @@
       <c r="K367" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L367" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>1593</v>
       </c>
@@ -21853,11 +20743,8 @@
       <c r="K368" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L368" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>1597</v>
       </c>
@@ -21891,11 +20778,8 @@
       <c r="K369" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L369" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>1601</v>
       </c>
@@ -21929,11 +20813,8 @@
       <c r="K370" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L370" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>1605</v>
       </c>
@@ -21967,11 +20848,8 @@
       <c r="K371" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L371" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>1609</v>
       </c>
@@ -22005,11 +20883,8 @@
       <c r="K372" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L372" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>1613</v>
       </c>
@@ -22043,11 +20918,8 @@
       <c r="K373" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L373" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>1617</v>
       </c>
@@ -22081,11 +20953,8 @@
       <c r="K374" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L374" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>1621</v>
       </c>
@@ -22119,11 +20988,8 @@
       <c r="K375" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L375" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>1625</v>
       </c>
@@ -22157,11 +21023,8 @@
       <c r="K376" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L376" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>1629</v>
       </c>
@@ -22195,11 +21058,8 @@
       <c r="K377" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L377" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>1633</v>
       </c>
@@ -22233,11 +21093,8 @@
       <c r="K378" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L378" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>1639</v>
       </c>
@@ -22271,11 +21128,8 @@
       <c r="K379" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L379" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>1643</v>
       </c>
@@ -22309,11 +21163,8 @@
       <c r="K380" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L380" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>1647</v>
       </c>
@@ -22347,11 +21198,8 @@
       <c r="K381" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L381" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>1651</v>
       </c>
@@ -22385,11 +21233,8 @@
       <c r="K382" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L382" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>1655</v>
       </c>
@@ -22423,11 +21268,8 @@
       <c r="K383" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L383" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>1659</v>
       </c>
@@ -22461,11 +21303,8 @@
       <c r="K384" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L384" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>1663</v>
       </c>
@@ -22499,11 +21338,8 @@
       <c r="K385" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L385" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>1667</v>
       </c>
@@ -22537,11 +21373,8 @@
       <c r="K386" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L386" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>1671</v>
       </c>
@@ -22575,11 +21408,8 @@
       <c r="K387" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L387" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>1675</v>
       </c>
@@ -22613,11 +21443,8 @@
       <c r="K388" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L388" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>1679</v>
       </c>
@@ -22651,11 +21478,8 @@
       <c r="K389" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L389" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>1683</v>
       </c>
@@ -22689,11 +21513,8 @@
       <c r="K390" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L390" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>1687</v>
       </c>
@@ -22727,11 +21548,8 @@
       <c r="K391" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L391" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>1691</v>
       </c>
@@ -22765,11 +21583,8 @@
       <c r="K392" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L392" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>1695</v>
       </c>
@@ -22803,11 +21618,8 @@
       <c r="K393" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L393" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>1699</v>
       </c>
@@ -22841,11 +21653,8 @@
       <c r="K394" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L394" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>1703</v>
       </c>
@@ -22879,11 +21688,8 @@
       <c r="K395" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L395" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>1707</v>
       </c>
@@ -22917,11 +21723,8 @@
       <c r="K396" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L396" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>1711</v>
       </c>
@@ -22955,11 +21758,8 @@
       <c r="K397" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L397" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>1715</v>
       </c>
@@ -22993,11 +21793,8 @@
       <c r="K398" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L398" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>1719</v>
       </c>
@@ -23031,11 +21828,8 @@
       <c r="K399" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L399" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>1723</v>
       </c>
@@ -23069,11 +21863,8 @@
       <c r="K400" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L400" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>1727</v>
       </c>
@@ -23107,11 +21898,8 @@
       <c r="K401" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L401" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>1731</v>
       </c>
@@ -23145,11 +21933,8 @@
       <c r="K402" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L402" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>1735</v>
       </c>
@@ -23183,11 +21968,8 @@
       <c r="K403" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L403" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>1739</v>
       </c>
@@ -23221,11 +22003,8 @@
       <c r="K404" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L404" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>1743</v>
       </c>
@@ -23259,11 +22038,8 @@
       <c r="K405" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L405" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>1747</v>
       </c>
@@ -23297,11 +22073,8 @@
       <c r="K406" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L406" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>1751</v>
       </c>
@@ -23335,11 +22108,8 @@
       <c r="K407" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L407" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>1757</v>
       </c>
@@ -23373,11 +22143,8 @@
       <c r="K408" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L408" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>1760</v>
       </c>
@@ -23411,11 +22178,8 @@
       <c r="K409" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L409" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>1763</v>
       </c>
@@ -23449,11 +22213,8 @@
       <c r="K410" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L410" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>1767</v>
       </c>
@@ -23487,11 +22248,8 @@
       <c r="K411" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L411" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>1771</v>
       </c>
@@ -23525,11 +22283,8 @@
       <c r="K412" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L412" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>1775</v>
       </c>
@@ -23563,11 +22318,8 @@
       <c r="K413" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L413" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>1779</v>
       </c>
@@ -23601,11 +22353,8 @@
       <c r="K414" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L414" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>1783</v>
       </c>
@@ -23639,11 +22388,8 @@
       <c r="K415" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L415" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>1787</v>
       </c>
@@ -23677,11 +22423,8 @@
       <c r="K416" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L416" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>1793</v>
       </c>
@@ -23715,11 +22458,8 @@
       <c r="K417" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L417" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>1797</v>
       </c>
@@ -23753,11 +22493,8 @@
       <c r="K418" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L418" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>1801</v>
       </c>
@@ -23791,11 +22528,8 @@
       <c r="K419" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L419" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>1805</v>
       </c>
@@ -23829,11 +22563,8 @@
       <c r="K420" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L420" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>1809</v>
       </c>
@@ -23867,11 +22598,8 @@
       <c r="K421" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L421" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>1813</v>
       </c>
@@ -23905,11 +22633,8 @@
       <c r="K422" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L422" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>1819</v>
       </c>
@@ -23943,11 +22668,8 @@
       <c r="K423" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L423" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>1825</v>
       </c>
@@ -23981,11 +22703,8 @@
       <c r="K424" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L424" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>1829</v>
       </c>
@@ -24019,11 +22738,8 @@
       <c r="K425" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L425" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>1833</v>
       </c>
@@ -24057,11 +22773,8 @@
       <c r="K426" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L426" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>1837</v>
       </c>
@@ -24095,11 +22808,8 @@
       <c r="K427" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L427" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>1841</v>
       </c>
@@ -24133,11 +22843,8 @@
       <c r="K428" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L428" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>1845</v>
       </c>
@@ -24171,11 +22878,8 @@
       <c r="K429" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L429" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>1849</v>
       </c>
@@ -24209,11 +22913,8 @@
       <c r="K430" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L430" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>1853</v>
       </c>
@@ -24247,11 +22948,8 @@
       <c r="K431" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L431" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>1857</v>
       </c>
@@ -24285,11 +22983,8 @@
       <c r="K432" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L432" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>1861</v>
       </c>
@@ -24323,11 +23018,8 @@
       <c r="K433" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L433" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>1865</v>
       </c>
@@ -24361,11 +23053,8 @@
       <c r="K434" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L434" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>1869</v>
       </c>
@@ -24399,11 +23088,8 @@
       <c r="K435" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L435" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>1873</v>
       </c>
@@ -24437,11 +23123,8 @@
       <c r="K436" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L436" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>1876</v>
       </c>
@@ -24475,11 +23158,8 @@
       <c r="K437" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L437" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>1880</v>
       </c>
@@ -24513,11 +23193,8 @@
       <c r="K438" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L438" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>1884</v>
       </c>
@@ -24551,11 +23228,8 @@
       <c r="K439" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L439" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>1888</v>
       </c>
@@ -24589,11 +23263,8 @@
       <c r="K440" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L440" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>1892</v>
       </c>
@@ -24627,11 +23298,8 @@
       <c r="K441" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L441" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>1898</v>
       </c>
@@ -24665,11 +23333,8 @@
       <c r="K442" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L442" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
         <v>1902</v>
       </c>
@@ -24703,11 +23368,8 @@
       <c r="K443" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L443" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>1906</v>
       </c>
@@ -24741,11 +23403,8 @@
       <c r="K444" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L444" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>1910</v>
       </c>
@@ -24779,11 +23438,8 @@
       <c r="K445" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L445" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>1914</v>
       </c>
@@ -24817,11 +23473,8 @@
       <c r="K446" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L446" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>1918</v>
       </c>
@@ -24855,11 +23508,8 @@
       <c r="K447" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L447" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
         <v>1922</v>
       </c>
@@ -24893,11 +23543,8 @@
       <c r="K448" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L448" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>1926</v>
       </c>
@@ -24931,11 +23578,8 @@
       <c r="K449" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L449" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>1930</v>
       </c>
@@ -24969,11 +23613,8 @@
       <c r="K450" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L450" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>1934</v>
       </c>
@@ -25007,11 +23648,8 @@
       <c r="K451" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L451" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
         <v>1938</v>
       </c>
@@ -25045,11 +23683,8 @@
       <c r="K452" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L452" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>1942</v>
       </c>
@@ -25083,11 +23718,8 @@
       <c r="K453" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L453" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>1946</v>
       </c>
@@ -25121,11 +23753,8 @@
       <c r="K454" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L454" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>1950</v>
       </c>
@@ -25159,11 +23788,8 @@
       <c r="K455" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L455" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>1954</v>
       </c>
@@ -25197,11 +23823,8 @@
       <c r="K456" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L456" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>1960</v>
       </c>
@@ -25235,11 +23858,8 @@
       <c r="K457" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L457" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
         <v>1963</v>
       </c>
@@ -25273,11 +23893,8 @@
       <c r="K458" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L458" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>1967</v>
       </c>
@@ -25311,11 +23928,8 @@
       <c r="K459" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L459" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>1971</v>
       </c>
@@ -25349,11 +23963,8 @@
       <c r="K460" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L460" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>1975</v>
       </c>
@@ -25387,11 +23998,8 @@
       <c r="K461" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L461" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>1979</v>
       </c>
@@ -25425,11 +24033,8 @@
       <c r="K462" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L462" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>1983</v>
       </c>
@@ -25463,11 +24068,8 @@
       <c r="K463" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L463" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>1987</v>
       </c>
@@ -25501,11 +24103,8 @@
       <c r="K464" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L464" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>1991</v>
       </c>
@@ -25539,11 +24138,8 @@
       <c r="K465" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L465" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>1995</v>
       </c>
@@ -25577,11 +24173,8 @@
       <c r="K466" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L466" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>1999</v>
       </c>
@@ -25615,11 +24208,8 @@
       <c r="K467" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L467" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>2003</v>
       </c>
@@ -25653,11 +24243,8 @@
       <c r="K468" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L468" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>2007</v>
       </c>
@@ -25691,11 +24278,8 @@
       <c r="K469" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L469" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>2011</v>
       </c>
@@ -25729,11 +24313,8 @@
       <c r="K470" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L470" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>2015</v>
       </c>
@@ -25767,11 +24348,8 @@
       <c r="K471" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L471" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>2019</v>
       </c>
@@ -25805,11 +24383,8 @@
       <c r="K472" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L472" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>2023</v>
       </c>
@@ -25843,11 +24418,8 @@
       <c r="K473" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L473" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>2027</v>
       </c>
@@ -25881,11 +24453,8 @@
       <c r="K474" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L474" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
         <v>2031</v>
       </c>
@@ -25919,11 +24488,8 @@
       <c r="K475" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L475" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
         <v>2035</v>
       </c>
@@ -25957,11 +24523,8 @@
       <c r="K476" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L476" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
         <v>2039</v>
       </c>
@@ -25995,11 +24558,8 @@
       <c r="K477" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L477" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
         <v>2043</v>
       </c>
@@ -26033,11 +24593,8 @@
       <c r="K478" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L478" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
         <v>2047</v>
       </c>
@@ -26071,11 +24628,8 @@
       <c r="K479" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L479" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>2053</v>
       </c>
@@ -26109,11 +24663,8 @@
       <c r="K480" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L480" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>2057</v>
       </c>
@@ -26147,11 +24698,8 @@
       <c r="K481" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L481" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>2061</v>
       </c>
@@ -26185,11 +24733,8 @@
       <c r="K482" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L482" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>2065</v>
       </c>
@@ -26223,11 +24768,8 @@
       <c r="K483" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L483" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>2071</v>
       </c>
@@ -26261,11 +24803,8 @@
       <c r="K484" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L484" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>2075</v>
       </c>
@@ -26299,11 +24838,8 @@
       <c r="K485" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L485" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>2079</v>
       </c>
@@ -26337,11 +24873,8 @@
       <c r="K486" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L486" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
         <v>2083</v>
       </c>
@@ -26375,11 +24908,8 @@
       <c r="K487" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L487" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
         <v>2087</v>
       </c>
@@ -26413,11 +24943,8 @@
       <c r="K488" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L488" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>2091</v>
       </c>
@@ -26451,11 +24978,8 @@
       <c r="K489" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L489" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>2095</v>
       </c>
@@ -26489,11 +25013,8 @@
       <c r="K490" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L490" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>2099</v>
       </c>
@@ -26527,11 +25048,8 @@
       <c r="K491" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L491" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
         <v>2103</v>
       </c>
@@ -26565,11 +25083,8 @@
       <c r="K492" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L492" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>2107</v>
       </c>
@@ -26603,11 +25118,8 @@
       <c r="K493" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L493" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
         <v>2111</v>
       </c>
@@ -26641,11 +25153,8 @@
       <c r="K494" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L494" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
         <v>2114</v>
       </c>
@@ -26679,11 +25188,8 @@
       <c r="K495" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L495" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
         <v>2118</v>
       </c>
@@ -26717,11 +25223,8 @@
       <c r="K496" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L496" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>2122</v>
       </c>
@@ -26755,11 +25258,8 @@
       <c r="K497" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L497" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>2126</v>
       </c>
@@ -26793,11 +25293,8 @@
       <c r="K498" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L498" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>2132</v>
       </c>
@@ -26831,11 +25328,8 @@
       <c r="K499" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L499" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>2136</v>
       </c>
@@ -26869,11 +25363,8 @@
       <c r="K500" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L500" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>2140</v>
       </c>
@@ -26907,11 +25398,8 @@
       <c r="K501" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L501" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>2144</v>
       </c>
@@ -26945,11 +25433,8 @@
       <c r="K502" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L502" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>2148</v>
       </c>
@@ -26983,11 +25468,8 @@
       <c r="K503" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L503" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>2152</v>
       </c>
@@ -27021,11 +25503,8 @@
       <c r="K504" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L504" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>2156</v>
       </c>
@@ -27059,11 +25538,8 @@
       <c r="K505" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L505" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
         <v>2160</v>
       </c>
@@ -27097,11 +25573,8 @@
       <c r="K506" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L506" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>2164</v>
       </c>
@@ -27135,11 +25608,8 @@
       <c r="K507" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L507" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
         <v>2168</v>
       </c>
@@ -27173,11 +25643,8 @@
       <c r="K508" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L508" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
         <v>2172</v>
       </c>
@@ -27211,11 +25678,8 @@
       <c r="K509" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L509" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
         <v>2176</v>
       </c>
@@ -27249,11 +25713,8 @@
       <c r="K510" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L510" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
         <v>2180</v>
       </c>
@@ -27287,11 +25748,8 @@
       <c r="K511" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L511" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>2184</v>
       </c>
@@ -27325,11 +25783,8 @@
       <c r="K512" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L512" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
         <v>2190</v>
       </c>
@@ -27363,11 +25818,8 @@
       <c r="K513" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L513" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
         <v>2194</v>
       </c>
@@ -27401,11 +25853,8 @@
       <c r="K514" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L514" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
         <v>2198</v>
       </c>
@@ -27439,11 +25888,8 @@
       <c r="K515" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L515" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
         <v>2202</v>
       </c>
@@ -27477,11 +25923,8 @@
       <c r="K516" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L516" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>2206</v>
       </c>
@@ -27515,11 +25958,8 @@
       <c r="K517" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L517" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
         <v>2210</v>
       </c>
@@ -27553,11 +25993,8 @@
       <c r="K518" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L518" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
         <v>2214</v>
       </c>
@@ -27591,11 +26028,8 @@
       <c r="K519" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L519" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
         <v>2218</v>
       </c>
@@ -27629,11 +26063,8 @@
       <c r="K520" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L520" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
         <v>2222</v>
       </c>
@@ -27667,11 +26098,8 @@
       <c r="K521" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L521" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
         <v>2226</v>
       </c>
@@ -27705,11 +26133,8 @@
       <c r="K522" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L522" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>2230</v>
       </c>
@@ -27743,11 +26168,8 @@
       <c r="K523" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L523" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
         <v>2234</v>
       </c>
@@ -27781,11 +26203,8 @@
       <c r="K524" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L524" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
         <v>2238</v>
       </c>
@@ -27819,11 +26238,8 @@
       <c r="K525" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L525" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
         <v>2242</v>
       </c>
@@ -27857,11 +26273,8 @@
       <c r="K526" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L526" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>2248</v>
       </c>
@@ -27895,11 +26308,8 @@
       <c r="K527" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L527" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
         <v>2252</v>
       </c>
@@ -27933,11 +26343,8 @@
       <c r="K528" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L528" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
         <v>2256</v>
       </c>
@@ -27971,11 +26378,8 @@
       <c r="K529" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L529" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
         <v>2259</v>
       </c>
@@ -28009,11 +26413,8 @@
       <c r="K530" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L530" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
         <v>2263</v>
       </c>
@@ -28047,11 +26448,8 @@
       <c r="K531" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L531" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
         <v>2267</v>
       </c>
@@ -28085,11 +26483,8 @@
       <c r="K532" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L532" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
         <v>2271</v>
       </c>
@@ -28123,11 +26518,8 @@
       <c r="K533" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L533" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
         <v>2275</v>
       </c>
@@ -28161,11 +26553,8 @@
       <c r="K534" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L534" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
         <v>2279</v>
       </c>
@@ -28199,11 +26588,8 @@
       <c r="K535" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L535" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
         <v>2283</v>
       </c>
@@ -28237,11 +26623,8 @@
       <c r="K536" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L536" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
         <v>2287</v>
       </c>
@@ -28275,11 +26658,8 @@
       <c r="K537" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L537" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
         <v>2291</v>
       </c>
@@ -28313,11 +26693,8 @@
       <c r="K538" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L538" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
         <v>2295</v>
       </c>
@@ -28351,11 +26728,8 @@
       <c r="K539" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L539" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
         <v>2299</v>
       </c>
@@ -28389,11 +26763,8 @@
       <c r="K540" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L540" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
         <v>2303</v>
       </c>
@@ -28427,11 +26798,8 @@
       <c r="K541" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L541" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
         <v>2307</v>
       </c>
@@ -28465,11 +26833,8 @@
       <c r="K542" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L542" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
         <v>2311</v>
       </c>
@@ -28503,11 +26868,8 @@
       <c r="K543" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L543" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
         <v>2315</v>
       </c>
@@ -28541,11 +26903,8 @@
       <c r="K544" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L544" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
         <v>2319</v>
       </c>
@@ -28579,11 +26938,8 @@
       <c r="K545" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L545" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
         <v>2323</v>
       </c>
@@ -28617,11 +26973,8 @@
       <c r="K546" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L546" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
         <v>2329</v>
       </c>
@@ -28655,11 +27008,8 @@
       <c r="K547" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L547" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
         <v>2333</v>
       </c>
@@ -28693,11 +27043,8 @@
       <c r="K548" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L548" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
         <v>2337</v>
       </c>
@@ -28731,11 +27078,8 @@
       <c r="K549" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L549" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
         <v>2341</v>
       </c>
@@ -28769,11 +27113,8 @@
       <c r="K550" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L550" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
         <v>2345</v>
       </c>
@@ -28807,11 +27148,8 @@
       <c r="K551" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L551" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
         <v>2349</v>
       </c>
@@ -28845,11 +27183,8 @@
       <c r="K552" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L552" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
         <v>2353</v>
       </c>
@@ -28883,11 +27218,8 @@
       <c r="K553" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L553" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
         <v>2357</v>
       </c>
@@ -28921,11 +27253,8 @@
       <c r="K554" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L554" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
         <v>2361</v>
       </c>
@@ -28959,11 +27288,8 @@
       <c r="K555" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L555" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
         <v>2365</v>
       </c>
@@ -28997,11 +27323,8 @@
       <c r="K556" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L556" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
         <v>2369</v>
       </c>
@@ -29035,11 +27358,8 @@
       <c r="K557" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L557" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
         <v>2373</v>
       </c>
@@ -29073,11 +27393,8 @@
       <c r="K558" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L558" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
         <v>2377</v>
       </c>
@@ -29111,11 +27428,8 @@
       <c r="K559" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L559" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
         <v>2381</v>
       </c>
@@ -29149,11 +27463,8 @@
       <c r="K560" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L560" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
         <v>2385</v>
       </c>
@@ -29187,11 +27498,8 @@
       <c r="K561" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L561" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
         <v>2389</v>
       </c>
@@ -29225,11 +27533,8 @@
       <c r="K562" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L562" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" s="2" t="s">
         <v>2395</v>
       </c>
@@ -29263,11 +27568,8 @@
       <c r="K563" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L563" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564" s="2" t="s">
         <v>2399</v>
       </c>
@@ -29301,11 +27603,8 @@
       <c r="K564" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L564" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565" s="2" t="s">
         <v>2403</v>
       </c>
@@ -29339,11 +27638,8 @@
       <c r="K565" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L565" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566" s="2" t="s">
         <v>2409</v>
       </c>
@@ -29377,11 +27673,8 @@
       <c r="K566" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L566" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567" s="2" t="s">
         <v>2413</v>
       </c>
@@ -29415,11 +27708,8 @@
       <c r="K567" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L567" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568" s="2" t="s">
         <v>2417</v>
       </c>
@@ -29453,11 +27743,8 @@
       <c r="K568" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L568" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569" s="2" t="s">
         <v>2421</v>
       </c>
@@ -29491,11 +27778,8 @@
       <c r="K569" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L569" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570" s="2" t="s">
         <v>2425</v>
       </c>
@@ -29529,11 +27813,8 @@
       <c r="K570" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L570" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571" s="2" t="s">
         <v>2431</v>
       </c>
@@ -29567,11 +27848,8 @@
       <c r="K571" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L571" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572" s="2" t="s">
         <v>2435</v>
       </c>
@@ -29605,11 +27883,8 @@
       <c r="K572" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L572" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573" s="2" t="s">
         <v>2439</v>
       </c>
@@ -29643,11 +27918,8 @@
       <c r="K573" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L573" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574" s="2" t="s">
         <v>2443</v>
       </c>
@@ -29681,11 +27953,8 @@
       <c r="K574" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L574" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575" s="2" t="s">
         <v>2447</v>
       </c>
@@ -29719,11 +27988,8 @@
       <c r="K575" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L575" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576" s="2" t="s">
         <v>2453</v>
       </c>
@@ -29757,11 +28023,8 @@
       <c r="K576" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L576" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577" s="2" t="s">
         <v>2457</v>
       </c>
@@ -29795,11 +28058,8 @@
       <c r="K577" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L577" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578" s="2" t="s">
         <v>2461</v>
       </c>
@@ -29833,11 +28093,8 @@
       <c r="K578" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L578" s="1" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579" s="2" t="s">
         <v>2465</v>
       </c>
@@ -29870,9 +28127,6 @@
       </c>
       <c r="K579" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="L579" s="1" t="s">
-        <v>2471</v>
       </c>
     </row>
   </sheetData>
